--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/88.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/88.xlsx
@@ -426,13 +426,13 @@
         <v>-13.34449372708938</v>
       </c>
       <c r="E2">
-        <v>-12.53840920982723</v>
+        <v>-8.329242432911721</v>
       </c>
       <c r="F2">
-        <v>-3.60555624650965</v>
+        <v>-2.622524365933449</v>
       </c>
       <c r="G2">
-        <v>-8.570907259836494</v>
+        <v>-8.210005700513168</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.75587730963791</v>
       </c>
       <c r="E3">
-        <v>-12.7655121813119</v>
+        <v>-10.08237321787118</v>
       </c>
       <c r="F3">
-        <v>-3.672908314929069</v>
+        <v>-2.807476441058703</v>
       </c>
       <c r="G3">
-        <v>-8.602659640867239</v>
+        <v>-7.353934995654043</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.0727374204224</v>
       </c>
       <c r="E4">
-        <v>-13.53818305887066</v>
+        <v>-10.28481864838409</v>
       </c>
       <c r="F4">
-        <v>-3.540025758008987</v>
+        <v>-2.599085710271237</v>
       </c>
       <c r="G4">
-        <v>-8.533629301699641</v>
+        <v>-8.149795284897358</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.36367013584547</v>
       </c>
       <c r="E5">
-        <v>-13.81991301230985</v>
+        <v>-12.0656093525824</v>
       </c>
       <c r="F5">
-        <v>-3.591402761065417</v>
+        <v>-2.937196291234897</v>
       </c>
       <c r="G5">
-        <v>-8.068624425959815</v>
+        <v>-7.121391542514636</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.59651423453508</v>
       </c>
       <c r="E6">
-        <v>-14.59994266013107</v>
+        <v>-12.16803437768789</v>
       </c>
       <c r="F6">
-        <v>-3.442139238754975</v>
+        <v>-2.486147755308358</v>
       </c>
       <c r="G6">
-        <v>-7.793710558823299</v>
+        <v>-6.803956325189276</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.782554540211502</v>
       </c>
       <c r="E7">
-        <v>-15.35392452546017</v>
+        <v>-12.48709707084632</v>
       </c>
       <c r="F7">
-        <v>-3.536482830627213</v>
+        <v>-2.606361261170024</v>
       </c>
       <c r="G7">
-        <v>-7.656263468919719</v>
+        <v>-6.528697929789018</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.915079187891029</v>
       </c>
       <c r="E8">
-        <v>-15.57995424860502</v>
+        <v>-13.17085588973848</v>
       </c>
       <c r="F8">
-        <v>-3.416222936190989</v>
+        <v>-2.386398237765449</v>
       </c>
       <c r="G8">
-        <v>-6.969569420959129</v>
+        <v>-7.058060685195794</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.011830850458784</v>
       </c>
       <c r="E9">
-        <v>-15.79237590735682</v>
+        <v>-13.78324595826975</v>
       </c>
       <c r="F9">
-        <v>-3.496130569334641</v>
+        <v>-2.798960824157924</v>
       </c>
       <c r="G9">
-        <v>-7.182382888861595</v>
+        <v>-6.863228311439086</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.094436667725971</v>
       </c>
       <c r="E10">
-        <v>-17.0325302136754</v>
+        <v>-14.26356308236731</v>
       </c>
       <c r="F10">
-        <v>-3.62212939313746</v>
+        <v>-2.347948736397107</v>
       </c>
       <c r="G10">
-        <v>-6.857919294955903</v>
+        <v>-4.573362221749401</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.18342934196214</v>
       </c>
       <c r="E11">
-        <v>-17.31035662251999</v>
+        <v>-13.68918502465642</v>
       </c>
       <c r="F11">
-        <v>-3.48613797335467</v>
+        <v>-2.457387667450562</v>
       </c>
       <c r="G11">
-        <v>-5.709540967473645</v>
+        <v>-4.503744543922663</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.307033498205702</v>
       </c>
       <c r="E12">
-        <v>-18.18597782816912</v>
+        <v>-14.70145293348701</v>
       </c>
       <c r="F12">
-        <v>-3.608361926902932</v>
+        <v>-2.330934069943606</v>
       </c>
       <c r="G12">
-        <v>-4.664393151473076</v>
+        <v>-4.952917525638169</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.476282931672639</v>
       </c>
       <c r="E13">
-        <v>-18.15675105692362</v>
+        <v>-15.7171488971414</v>
       </c>
       <c r="F13">
-        <v>-3.582636977208993</v>
+        <v>-1.85489783131162</v>
       </c>
       <c r="G13">
-        <v>-4.428719412965959</v>
+        <v>-3.46128076715772</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.715638483283969</v>
       </c>
       <c r="E14">
-        <v>-19.64239393919801</v>
+        <v>-17.41898112854198</v>
       </c>
       <c r="F14">
-        <v>-3.371544111953595</v>
+        <v>-1.789480000777737</v>
       </c>
       <c r="G14">
-        <v>-4.035392822192202</v>
+        <v>-3.30067153426602</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.039942127933014</v>
       </c>
       <c r="E15">
-        <v>-20.80124402318287</v>
+        <v>-17.82809705581694</v>
       </c>
       <c r="F15">
-        <v>-3.080418530076723</v>
+        <v>-1.813962399367476</v>
       </c>
       <c r="G15">
-        <v>-2.468507809689008</v>
+        <v>-3.051810566311495</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.467566734919709</v>
       </c>
       <c r="E16">
-        <v>-21.15908403926899</v>
+        <v>-17.92995149319746</v>
       </c>
       <c r="F16">
-        <v>-2.87216199480851</v>
+        <v>-1.801801137526977</v>
       </c>
       <c r="G16">
-        <v>-2.869125274767851</v>
+        <v>-3.175017154647084</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.01928139083771</v>
       </c>
       <c r="E17">
-        <v>-22.8758149501548</v>
+        <v>-18.65165439579989</v>
       </c>
       <c r="F17">
-        <v>-2.610886632291519</v>
+        <v>-1.474770798943163</v>
       </c>
       <c r="G17">
-        <v>-2.096249942548445</v>
+        <v>-2.318424735560006</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.705326935449804</v>
       </c>
       <c r="E18">
-        <v>-24.18958865841607</v>
+        <v>-20.62187116773905</v>
       </c>
       <c r="F18">
-        <v>-2.480908331485651</v>
+        <v>-1.480142761550318</v>
       </c>
       <c r="G18">
-        <v>-1.740191466246862</v>
+        <v>-1.988550407302792</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.536636618499206</v>
       </c>
       <c r="E19">
-        <v>-24.98496530464929</v>
+        <v>-22.08680986685037</v>
       </c>
       <c r="F19">
-        <v>-1.896242476752746</v>
+        <v>-1.071826386464594</v>
       </c>
       <c r="G19">
-        <v>-1.408210593748483</v>
+        <v>-2.288493432494752</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.506502381015772</v>
       </c>
       <c r="E20">
-        <v>-25.54641456906828</v>
+        <v>-22.00432371280066</v>
       </c>
       <c r="F20">
-        <v>-1.896049467147893</v>
+        <v>-0.6431967859274202</v>
       </c>
       <c r="G20">
-        <v>-0.5588795179724561</v>
+        <v>-0.8091514111975423</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.603938109741265</v>
       </c>
       <c r="E21">
-        <v>-25.46300460632099</v>
+        <v>-22.13046888475833</v>
       </c>
       <c r="F21">
-        <v>-1.891390728874549</v>
+        <v>-0.4087124819517698</v>
       </c>
       <c r="G21">
-        <v>-0.7044837246728154</v>
+        <v>-1.055590837641197</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.806253056799455</v>
       </c>
       <c r="E22">
-        <v>-25.45963089318528</v>
+        <v>-24.19353748775076</v>
       </c>
       <c r="F22">
-        <v>-1.394406735360569</v>
+        <v>-0.3386748464124744</v>
       </c>
       <c r="G22">
-        <v>-2.002515286259788</v>
+        <v>-0.3550565971428692</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.082580320650542</v>
       </c>
       <c r="E23">
-        <v>-26.54519668230402</v>
+        <v>-23.88548804337899</v>
       </c>
       <c r="F23">
-        <v>-1.405921870626885</v>
+        <v>-0.3589657059440483</v>
       </c>
       <c r="G23">
-        <v>-1.206540154261892</v>
+        <v>-1.141125721252802</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.400153094216077</v>
       </c>
       <c r="E24">
-        <v>-26.75216605835058</v>
+        <v>-25.55654929389744</v>
       </c>
       <c r="F24">
-        <v>-1.35225940190613</v>
+        <v>-0.3962488660092485</v>
       </c>
       <c r="G24">
-        <v>-1.273772384014914</v>
+        <v>-1.754110408102026</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.721364987916323</v>
       </c>
       <c r="E25">
-        <v>-27.81583214716823</v>
+        <v>-24.18861956497843</v>
       </c>
       <c r="F25">
-        <v>-1.057118723227888</v>
+        <v>0.1055338598691493</v>
       </c>
       <c r="G25">
-        <v>-2.340694386283958</v>
+        <v>-1.207685300586138</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.013037570697098</v>
       </c>
       <c r="E26">
-        <v>-27.49522524437318</v>
+        <v>-24.73483957130962</v>
       </c>
       <c r="F26">
-        <v>-1.147264149102739</v>
+        <v>0.2481762415290157</v>
       </c>
       <c r="G26">
-        <v>-1.998541726951301</v>
+        <v>-0.6154904335375557</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.243529536288653</v>
       </c>
       <c r="E27">
-        <v>-28.00307096196337</v>
+        <v>-25.56444695256682</v>
       </c>
       <c r="F27">
-        <v>-0.6828349945187794</v>
+        <v>0.002322594949942062</v>
       </c>
       <c r="G27">
-        <v>-2.54631869774968</v>
+        <v>-1.440058130204454</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.388864208801594</v>
       </c>
       <c r="E28">
-        <v>-27.56080660495227</v>
+        <v>-25.65219972188745</v>
       </c>
       <c r="F28">
-        <v>-1.144021919088182</v>
+        <v>0.1622927659415686</v>
       </c>
       <c r="G28">
-        <v>-2.065534427530483</v>
+        <v>-2.641575840841919</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.431284495078354</v>
       </c>
       <c r="E29">
-        <v>-27.07988719381168</v>
+        <v>-24.21217215829233</v>
       </c>
       <c r="F29">
-        <v>-1.095102682115857</v>
+        <v>-0.2432055032398314</v>
       </c>
       <c r="G29">
-        <v>-2.879579246656242</v>
+        <v>-2.769284265157067</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.360934403446762</v>
       </c>
       <c r="E30">
-        <v>-27.46305043654868</v>
+        <v>-25.09483966949739</v>
       </c>
       <c r="F30">
-        <v>-1.02300821031541</v>
+        <v>0.0915559883143104</v>
       </c>
       <c r="G30">
-        <v>-3.38481517993642</v>
+        <v>-2.931960667631217</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.176775133804173</v>
       </c>
       <c r="E31">
-        <v>-27.24285338792571</v>
+        <v>-24.29447717338174</v>
       </c>
       <c r="F31">
-        <v>-0.8125051426508056</v>
+        <v>-0.1949920352946918</v>
       </c>
       <c r="G31">
-        <v>-2.907925719708285</v>
+        <v>-1.547462355509757</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.883722663047275</v>
       </c>
       <c r="E32">
-        <v>-28.26690891459826</v>
+        <v>-23.06142351430718</v>
       </c>
       <c r="F32">
-        <v>-0.9077317741744284</v>
+        <v>0.05762026092382306</v>
       </c>
       <c r="G32">
-        <v>-3.645665731469157</v>
+        <v>-2.854221966444853</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.496749402635233</v>
       </c>
       <c r="E33">
-        <v>-27.30982499002515</v>
+        <v>-24.78813971037991</v>
       </c>
       <c r="F33">
-        <v>-1.173853085997798</v>
+        <v>0.2075671863415756</v>
       </c>
       <c r="G33">
-        <v>-3.453084275702227</v>
+        <v>-2.488752946710782</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.033962940843826</v>
       </c>
       <c r="E34">
-        <v>-26.06545920287943</v>
+        <v>-22.88594514650995</v>
       </c>
       <c r="F34">
-        <v>-1.066820562249476</v>
+        <v>-0.4147587356248034</v>
       </c>
       <c r="G34">
-        <v>-2.821698498347637</v>
+        <v>-3.387584530932592</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.521575003047597</v>
       </c>
       <c r="E35">
-        <v>-26.52674767919677</v>
+        <v>-24.0056963859126</v>
       </c>
       <c r="F35">
-        <v>-0.9839498589060109</v>
+        <v>-0.04024637751252173</v>
       </c>
       <c r="G35">
-        <v>-3.602491418189983</v>
+        <v>-2.770911751050552</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.9877076310011114</v>
       </c>
       <c r="E36">
-        <v>-25.89981668062687</v>
+        <v>-21.89100770770672</v>
       </c>
       <c r="F36">
-        <v>-0.9049882213363565</v>
+        <v>-0.1235793098667492</v>
       </c>
       <c r="G36">
-        <v>-3.546556434266129</v>
+        <v>-2.301539569415104</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.4624902503326284</v>
       </c>
       <c r="E37">
-        <v>-25.06303166806752</v>
+        <v>-22.69180040885311</v>
       </c>
       <c r="F37">
-        <v>-1.268918185877874</v>
+        <v>-0.2369306201636251</v>
       </c>
       <c r="G37">
-        <v>-3.202530197423028</v>
+        <v>-2.227741615321633</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.02252327239739975</v>
       </c>
       <c r="E38">
-        <v>-24.77744345477378</v>
+        <v>-21.56877055426892</v>
       </c>
       <c r="F38">
-        <v>-0.9468307155865651</v>
+        <v>-0.2068534281353779</v>
       </c>
       <c r="G38">
-        <v>-4.362937483142212</v>
+        <v>-2.588948328249986</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.4409783312121465</v>
       </c>
       <c r="E39">
-        <v>-23.92689640970513</v>
+        <v>-21.15983576595426</v>
       </c>
       <c r="F39">
-        <v>-0.839722810404589</v>
+        <v>0.0270593023323409</v>
       </c>
       <c r="G39">
-        <v>-3.855381726219506</v>
+        <v>-1.235037563505669</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.7676557860675429</v>
       </c>
       <c r="E40">
-        <v>-24.01035618566649</v>
+        <v>-20.95805602112048</v>
       </c>
       <c r="F40">
-        <v>-1.030075012628693</v>
+        <v>0.3726011672665155</v>
       </c>
       <c r="G40">
-        <v>-4.326447018179627</v>
+        <v>-2.142393761338917</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.9854142738239884</v>
       </c>
       <c r="E41">
-        <v>-22.68102716918886</v>
+        <v>-21.19991276092214</v>
       </c>
       <c r="F41">
-        <v>-0.6713679045618258</v>
+        <v>0.07189717311107253</v>
       </c>
       <c r="G41">
-        <v>-4.45294139051778</v>
+        <v>-1.92279144602996</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.082632009952698</v>
       </c>
       <c r="E42">
-        <v>-22.67250005263242</v>
+        <v>-19.73748283641107</v>
       </c>
       <c r="F42">
-        <v>-0.6263154866257692</v>
+        <v>0.1192184893633971</v>
       </c>
       <c r="G42">
-        <v>-3.693558441350811</v>
+        <v>-2.222537597928353</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.054395076364006</v>
       </c>
       <c r="E43">
-        <v>-22.32238561320339</v>
+        <v>-19.50497286696124</v>
       </c>
       <c r="F43">
-        <v>-0.9966363056798854</v>
+        <v>0.08416198087692202</v>
       </c>
       <c r="G43">
-        <v>-3.594675548435386</v>
+        <v>-2.545114489437364</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.9049320560039599</v>
       </c>
       <c r="E44">
-        <v>-21.57149669562153</v>
+        <v>-18.88948985068273</v>
       </c>
       <c r="F44">
-        <v>-0.941344438277824</v>
+        <v>-0.02043348597236316</v>
       </c>
       <c r="G44">
-        <v>-3.578111942003309</v>
+        <v>-2.457709309536875</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.6447181815315319</v>
       </c>
       <c r="E45">
-        <v>-21.62025477526212</v>
+        <v>-19.55395737030221</v>
       </c>
       <c r="F45">
-        <v>-0.9261902850110098</v>
+        <v>-0.229779324375257</v>
       </c>
       <c r="G45">
-        <v>-3.441147191668967</v>
+        <v>-1.462623090868755</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.2922389556234716</v>
       </c>
       <c r="E46">
-        <v>-21.6965776761874</v>
+        <v>-18.66868145806873</v>
       </c>
       <c r="F46">
-        <v>-1.209167216746543</v>
+        <v>0.1748856071989267</v>
       </c>
       <c r="G46">
-        <v>-3.559527103090613</v>
+        <v>-2.661184420881161</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.1267898427112691</v>
       </c>
       <c r="E47">
-        <v>-20.24869321018896</v>
+        <v>-17.77146848835102</v>
       </c>
       <c r="F47">
-        <v>-1.115458154304849</v>
+        <v>-0.4688121937596795</v>
       </c>
       <c r="G47">
-        <v>-3.708675029075173</v>
+        <v>-1.706972379179043</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.5864112322510399</v>
       </c>
       <c r="E48">
-        <v>-20.12635648487175</v>
+        <v>-17.34268086998674</v>
       </c>
       <c r="F48">
-        <v>-1.17375616701167</v>
+        <v>-0.1160560771145241</v>
       </c>
       <c r="G48">
-        <v>-2.929650687653368</v>
+        <v>-2.334315691572397</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.056893969577023</v>
       </c>
       <c r="E49">
-        <v>-19.01850607516126</v>
+        <v>-18.495268074419</v>
       </c>
       <c r="F49">
-        <v>-1.268809669748108</v>
+        <v>-0.2995949574506022</v>
       </c>
       <c r="G49">
-        <v>-4.149831986520955</v>
+        <v>-1.642676842721724</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.51406628986026</v>
       </c>
       <c r="E50">
-        <v>-18.98092426937161</v>
+        <v>-16.27280171483057</v>
       </c>
       <c r="F50">
-        <v>-0.9487856626571719</v>
+        <v>-0.3938018687013787</v>
       </c>
       <c r="G50">
-        <v>-2.981392270424252</v>
+        <v>-2.170481017887763</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.937428586270262</v>
       </c>
       <c r="E51">
-        <v>-18.56598472452278</v>
+        <v>-15.50767527496859</v>
       </c>
       <c r="F51">
-        <v>-1.047223046234045</v>
+        <v>-0.5323198090627065</v>
       </c>
       <c r="G51">
-        <v>-3.373481840670098</v>
+        <v>-1.903012242469627</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.311379785378329</v>
       </c>
       <c r="E52">
-        <v>-18.68132948597215</v>
+        <v>-16.87080934991348</v>
       </c>
       <c r="F52">
-        <v>-1.085632785967053</v>
+        <v>-0.2942569579069622</v>
       </c>
       <c r="G52">
-        <v>-3.718364476340213</v>
+        <v>-1.813523486878891</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.629494101791658</v>
       </c>
       <c r="E53">
-        <v>-17.45514099349322</v>
+        <v>-15.30497624991126</v>
       </c>
       <c r="F53">
-        <v>-1.400531683936868</v>
+        <v>0.02911116838907528</v>
       </c>
       <c r="G53">
-        <v>-4.093762472513164</v>
+        <v>-2.058181210015768</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.886631711612972</v>
       </c>
       <c r="E54">
-        <v>-17.33442093339675</v>
+        <v>-14.32433973202425</v>
       </c>
       <c r="F54">
-        <v>-1.32967644977101</v>
+        <v>-0.9409840984576061</v>
       </c>
       <c r="G54">
-        <v>-3.963484851716971</v>
+        <v>-2.572299410057363</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.088647597800558</v>
       </c>
       <c r="E55">
-        <v>-17.4579622328</v>
+        <v>-14.98866234047549</v>
       </c>
       <c r="F55">
-        <v>-1.107347609064039</v>
+        <v>-0.2785834182785927</v>
       </c>
       <c r="G55">
-        <v>-3.651775366012842</v>
+        <v>-2.754561424019839</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.239770289786279</v>
       </c>
       <c r="E56">
-        <v>-16.19302358823744</v>
+        <v>-14.69749504720431</v>
       </c>
       <c r="F56">
-        <v>-1.44673967439983</v>
+        <v>-0.3652654400423386</v>
       </c>
       <c r="G56">
-        <v>-3.85027286425145</v>
+        <v>-3.33553451333512</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.349885502436096</v>
       </c>
       <c r="E57">
-        <v>-15.98095515045824</v>
+        <v>-14.66701841713269</v>
       </c>
       <c r="F57">
-        <v>-1.38830580943895</v>
+        <v>-0.4390854011428165</v>
       </c>
       <c r="G57">
-        <v>-4.065694903293674</v>
+        <v>-2.926001969279266</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.428490655644739</v>
       </c>
       <c r="E58">
-        <v>-16.40924010820767</v>
+        <v>-13.64716984281326</v>
       </c>
       <c r="F58">
-        <v>-1.20671027902984</v>
+        <v>-0.435868850517746</v>
       </c>
       <c r="G58">
-        <v>-4.389958342684239</v>
+        <v>-3.501252608194875</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.484367685923682</v>
       </c>
       <c r="E59">
-        <v>-15.47403324156561</v>
+        <v>-13.79842540314346</v>
       </c>
       <c r="F59">
-        <v>-1.455815267664902</v>
+        <v>-0.6493656379760682</v>
       </c>
       <c r="G59">
-        <v>-4.619305886024747</v>
+        <v>-2.981966484197155</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.527004068208169</v>
       </c>
       <c r="E60">
-        <v>-15.93742745829651</v>
+        <v>-13.82828616075004</v>
       </c>
       <c r="F60">
-        <v>-1.350435336885165</v>
+        <v>-0.6047555682331064</v>
       </c>
       <c r="G60">
-        <v>-4.855498057538255</v>
+        <v>-3.242423289142757</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.56174771633974</v>
       </c>
       <c r="E61">
-        <v>-15.07891482744836</v>
+        <v>-11.80708329995851</v>
       </c>
       <c r="F61">
-        <v>-1.096919291830196</v>
+        <v>-0.4011718534840859</v>
       </c>
       <c r="G61">
-        <v>-5.433367111258302</v>
+        <v>-3.733257940998533</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.596119092991804</v>
       </c>
       <c r="E62">
-        <v>-15.62057918892783</v>
+        <v>-12.76561633621408</v>
       </c>
       <c r="F62">
-        <v>-1.773479256025262</v>
+        <v>-0.7481401670858813</v>
       </c>
       <c r="G62">
-        <v>-5.29316051402323</v>
+        <v>-4.170293684165653</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.632162342275114</v>
       </c>
       <c r="E63">
-        <v>-15.06561469928783</v>
+        <v>-12.35304518327126</v>
       </c>
       <c r="F63">
-        <v>-1.233153423262006</v>
+        <v>-0.6768442414617334</v>
       </c>
       <c r="G63">
-        <v>-5.687484596151057</v>
+        <v>-4.046903347422734</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.672591668734468</v>
       </c>
       <c r="E64">
-        <v>-15.23551398710761</v>
+        <v>-12.49516681152799</v>
       </c>
       <c r="F64">
-        <v>-1.793080085510304</v>
+        <v>-0.259898763141047</v>
       </c>
       <c r="G64">
-        <v>-5.246636073531863</v>
+        <v>-4.057081696700132</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.715414482269224</v>
       </c>
       <c r="E65">
-        <v>-14.70175634124553</v>
+        <v>-11.98471722138339</v>
       </c>
       <c r="F65">
-        <v>-1.666651339025432</v>
+        <v>-0.6556488047263025</v>
       </c>
       <c r="G65">
-        <v>-5.153272195279422</v>
+        <v>-5.274090054319736</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.758775633804848</v>
       </c>
       <c r="E66">
-        <v>-14.97634036270062</v>
+        <v>-11.9876788433844</v>
       </c>
       <c r="F66">
-        <v>-1.425347914589936</v>
+        <v>-0.9087009640357038</v>
       </c>
       <c r="G66">
-        <v>-5.534619046139647</v>
+        <v>-4.306431566667015</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.799033397007191</v>
       </c>
       <c r="E67">
-        <v>-14.2411244936593</v>
+        <v>-11.5240446175311</v>
       </c>
       <c r="F67">
-        <v>-1.771187163421716</v>
+        <v>-0.6872510211431035</v>
       </c>
       <c r="G67">
-        <v>-6.084801152341099</v>
+        <v>-4.427269113036685</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.832565398025989</v>
       </c>
       <c r="E68">
-        <v>-13.76015526930463</v>
+        <v>-11.19438076672071</v>
       </c>
       <c r="F68">
-        <v>-1.949474194424045</v>
+        <v>-1.059698259320206</v>
       </c>
       <c r="G68">
-        <v>-6.528665117573423</v>
+        <v>-5.714981232819204</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.858151456554419</v>
       </c>
       <c r="E69">
-        <v>-14.89252283729265</v>
+        <v>-10.73583201717802</v>
       </c>
       <c r="F69">
-        <v>-1.74351306522899</v>
+        <v>-1.262217521956629</v>
       </c>
       <c r="G69">
-        <v>-6.210859122211846</v>
+        <v>-4.411155033958252</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.872908228714941</v>
       </c>
       <c r="E70">
-        <v>-14.23271964590107</v>
+        <v>-10.98210854761116</v>
       </c>
       <c r="F70">
-        <v>-2.052458486674885</v>
+        <v>-1.248437630211059</v>
       </c>
       <c r="G70">
-        <v>-5.5328832799347</v>
+        <v>-4.742036697234217</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.878218456511506</v>
       </c>
       <c r="E71">
-        <v>-14.28370573475343</v>
+        <v>-10.95867369462147</v>
       </c>
       <c r="F71">
-        <v>-2.055245114617902</v>
+        <v>-0.9123184444837292</v>
       </c>
       <c r="G71">
-        <v>-6.162041107850428</v>
+        <v>-5.020402409451268</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.873853328709933</v>
       </c>
       <c r="E72">
-        <v>-13.80096587706176</v>
+        <v>-11.08193875711025</v>
       </c>
       <c r="F72">
-        <v>-2.305154448001082</v>
+        <v>-1.054828287359148</v>
       </c>
       <c r="G72">
-        <v>-6.238887316772623</v>
+        <v>-5.146233975034414</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.862455818705516</v>
       </c>
       <c r="E73">
-        <v>-14.43399220164598</v>
+        <v>-11.65766630007543</v>
       </c>
       <c r="F73">
-        <v>-2.406126635830522</v>
+        <v>-1.237291946806392</v>
       </c>
       <c r="G73">
-        <v>-6.464615672733062</v>
+        <v>-4.632489834250595</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.846644683226519</v>
       </c>
       <c r="E74">
-        <v>-13.96872772514992</v>
+        <v>-11.60715570099387</v>
       </c>
       <c r="F74">
-        <v>-2.757081881741992</v>
+        <v>-1.393260274875094</v>
       </c>
       <c r="G74">
-        <v>-5.794905227564159</v>
+        <v>-5.579210847132501</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.828423737725109</v>
       </c>
       <c r="E75">
-        <v>-14.55847089516883</v>
+        <v>-10.72245943343337</v>
       </c>
       <c r="F75">
-        <v>-2.859573295388167</v>
+        <v>-1.197697641687381</v>
       </c>
       <c r="G75">
-        <v>-5.618191759258703</v>
+        <v>-4.536464885313445</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.810957212814849</v>
       </c>
       <c r="E76">
-        <v>-14.68075780727196</v>
+        <v>-12.24684341084338</v>
       </c>
       <c r="F76">
-        <v>-2.375153150272446</v>
+        <v>-1.9363230335372</v>
       </c>
       <c r="G76">
-        <v>-6.066957869500839</v>
+        <v>-4.69072495448762</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.794761137947565</v>
       </c>
       <c r="E77">
-        <v>-14.90723584934357</v>
+        <v>-12.44270444014913</v>
       </c>
       <c r="F77">
-        <v>-2.630413737077711</v>
+        <v>-1.53617187594087</v>
       </c>
       <c r="G77">
-        <v>-5.668906319681481</v>
+        <v>-4.176311444505675</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.782972434185126</v>
       </c>
       <c r="E78">
-        <v>-15.3421912493063</v>
+        <v>-12.23465728728874</v>
       </c>
       <c r="F78">
-        <v>-2.410222084269963</v>
+        <v>-1.471362067080643</v>
       </c>
       <c r="G78">
-        <v>-5.041274259790896</v>
+        <v>-4.201727786705133</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.773965360111984</v>
       </c>
       <c r="E79">
-        <v>-16.03823128970726</v>
+        <v>-13.40114690692455</v>
       </c>
       <c r="F79">
-        <v>-2.774070040438604</v>
+        <v>-1.58706014222965</v>
       </c>
       <c r="G79">
-        <v>-5.369829536981214</v>
+        <v>-4.189492111509964</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.766023174347655</v>
       </c>
       <c r="E80">
-        <v>-16.09968721046535</v>
+        <v>-14.3752578937665</v>
       </c>
       <c r="F80">
-        <v>-2.931846694547617</v>
+        <v>-1.661836867680361</v>
       </c>
       <c r="G80">
-        <v>-4.771416755077484</v>
+        <v>-3.993829588698716</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.752880684720323</v>
       </c>
       <c r="E81">
-        <v>-17.343423539724</v>
+        <v>-13.93041683504502</v>
       </c>
       <c r="F81">
-        <v>-2.798097665324207</v>
+        <v>-1.635244617315691</v>
       </c>
       <c r="G81">
-        <v>-4.796039041659558</v>
+        <v>-2.941154650440781</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.726980648777702</v>
       </c>
       <c r="E82">
-        <v>-16.99349476772928</v>
+        <v>-14.44295405170716</v>
       </c>
       <c r="F82">
-        <v>-2.662497234955539</v>
+        <v>-2.020079261634258</v>
       </c>
       <c r="G82">
-        <v>-4.965044920521876</v>
+        <v>-2.690636665598737</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.681021027374185</v>
       </c>
       <c r="E83">
-        <v>-17.56270583659742</v>
+        <v>-16.00036871852912</v>
       </c>
       <c r="F83">
-        <v>-3.213993602145546</v>
+        <v>-1.87478527591803</v>
       </c>
       <c r="G83">
-        <v>-5.059635975637549</v>
+        <v>-4.028193822090781</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.606900558583027</v>
       </c>
       <c r="E84">
-        <v>-18.63258952022759</v>
+        <v>-15.37803412107701</v>
       </c>
       <c r="F84">
-        <v>-2.970556303280438</v>
+        <v>-1.525219202141056</v>
       </c>
       <c r="G84">
-        <v>-4.793594531597771</v>
+        <v>-3.201640986380419</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.50160634540367</v>
       </c>
       <c r="E85">
-        <v>-20.62241458461997</v>
+        <v>-17.81099300948997</v>
       </c>
       <c r="F85">
-        <v>-2.91661467474494</v>
+        <v>-2.044708281254293</v>
       </c>
       <c r="G85">
-        <v>-4.651196078360989</v>
+        <v>-2.828155942376624</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.362981758030924</v>
       </c>
       <c r="E86">
-        <v>-20.96637029939857</v>
+        <v>-17.29876372906035</v>
       </c>
       <c r="F86">
-        <v>-2.752791766962893</v>
+        <v>-2.04275167744888</v>
       </c>
       <c r="G86">
-        <v>-4.273609507407889</v>
+        <v>-2.665112043087817</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.196578053020958</v>
       </c>
       <c r="E87">
-        <v>-21.28186002656495</v>
+        <v>-20.99095991326022</v>
       </c>
       <c r="F87">
-        <v>-3.043941371494447</v>
+        <v>-2.199900429066572</v>
       </c>
       <c r="G87">
-        <v>-4.256570123849692</v>
+        <v>-3.416698809829545</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.013662323533958</v>
       </c>
       <c r="E88">
-        <v>-22.99935624955805</v>
+        <v>-21.08331361217265</v>
       </c>
       <c r="F88">
-        <v>-2.704238668382606</v>
+        <v>-2.265498015326862</v>
       </c>
       <c r="G88">
-        <v>-4.419561523593549</v>
+        <v>-2.305821563550179</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.82886495235863</v>
       </c>
       <c r="E89">
-        <v>-24.67004163673387</v>
+        <v>-22.2371959601711</v>
       </c>
       <c r="F89">
-        <v>-2.723939730323386</v>
+        <v>-2.06243782877641</v>
       </c>
       <c r="G89">
-        <v>-4.319034738676842</v>
+        <v>-2.782697898892077</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.663631674948329</v>
       </c>
       <c r="E90">
-        <v>-25.62852938824936</v>
+        <v>-23.65821751835604</v>
       </c>
       <c r="F90">
-        <v>-2.379449891990767</v>
+        <v>-2.447866412522784</v>
       </c>
       <c r="G90">
-        <v>-4.503324547563054</v>
+        <v>-3.503188528914948</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.539411808586754</v>
       </c>
       <c r="E91">
-        <v>-27.66147005366877</v>
+        <v>-24.98508304497349</v>
       </c>
       <c r="F91">
-        <v>-2.760999231189831</v>
+        <v>-2.698111234704098</v>
       </c>
       <c r="G91">
-        <v>-4.969156291135861</v>
+        <v>-2.428263627262418</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.481477706707864</v>
       </c>
       <c r="E92">
-        <v>-29.17347318314181</v>
+        <v>-26.6347472558057</v>
       </c>
       <c r="F92">
-        <v>-3.029796169724242</v>
+        <v>-2.200259112151984</v>
       </c>
       <c r="G92">
-        <v>-4.048271616813023</v>
+        <v>-2.591172996467289</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.51255866441032</v>
       </c>
       <c r="E93">
-        <v>-31.29247070436598</v>
+        <v>-30.47930394799363</v>
       </c>
       <c r="F93">
-        <v>-3.18247587920383</v>
+        <v>-2.437613709178335</v>
       </c>
       <c r="G93">
-        <v>-4.689481371516591</v>
+        <v>-3.480961534071269</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.648846430096195</v>
       </c>
       <c r="E94">
-        <v>-33.69930029775468</v>
+        <v>-30.19561995802013</v>
       </c>
       <c r="F94">
-        <v>-2.648018201122006</v>
+        <v>-2.226467828409157</v>
       </c>
       <c r="G94">
-        <v>-4.978402773490376</v>
+        <v>-2.837431955725175</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.901712841304987</v>
       </c>
       <c r="E95">
-        <v>-35.64662110511107</v>
+        <v>-34.83325056740838</v>
       </c>
       <c r="F95">
-        <v>-2.876827360021077</v>
+        <v>-2.41615982181323</v>
       </c>
       <c r="G95">
-        <v>-5.19524230024628</v>
+        <v>-3.091132725479881</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.277194664809289</v>
       </c>
       <c r="E96">
-        <v>-39.25850253854789</v>
+        <v>-35.62980461688358</v>
       </c>
       <c r="F96">
-        <v>-2.412495952790648</v>
+        <v>-2.545800977086158</v>
       </c>
       <c r="G96">
-        <v>-5.400315366490015</v>
+        <v>-3.561282556624917</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.761383893817802</v>
       </c>
       <c r="E97">
-        <v>-40.50962028043904</v>
+        <v>-38.37281453517971</v>
       </c>
       <c r="F97">
-        <v>-2.434414554268723</v>
+        <v>-2.128740355696483</v>
       </c>
       <c r="G97">
-        <v>-5.592063391980846</v>
+        <v>-4.847839686418511</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.360284839750008</v>
       </c>
       <c r="E98">
-        <v>-42.87077115651238</v>
+        <v>-41.39762233402515</v>
       </c>
       <c r="F98">
-        <v>-2.72569255574771</v>
+        <v>-2.118936627484351</v>
       </c>
       <c r="G98">
-        <v>-5.975326476231785</v>
+        <v>-3.602068140608814</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.025173454595622</v>
       </c>
       <c r="E99">
-        <v>-44.66133883609325</v>
+        <v>-43.1685183225167</v>
       </c>
       <c r="F99">
-        <v>-2.426989897237431</v>
+        <v>-2.56562380903515</v>
       </c>
       <c r="G99">
-        <v>-6.081451025128906</v>
+        <v>-3.743866130300218</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.786511053790737</v>
       </c>
       <c r="E100">
-        <v>-46.45628555003955</v>
+        <v>-45.94038367718971</v>
       </c>
       <c r="F100">
-        <v>-2.239409412343094</v>
+        <v>-2.387826343167876</v>
       </c>
       <c r="G100">
-        <v>-6.803359142865457</v>
+        <v>-4.117311799645299</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.540921743137408</v>
       </c>
       <c r="E101">
-        <v>-49.96357847991372</v>
+        <v>-47.32846058696884</v>
       </c>
       <c r="F101">
-        <v>-2.327049026824476</v>
+        <v>-2.479454546693737</v>
       </c>
       <c r="G101">
-        <v>-7.022780990988644</v>
+        <v>-5.062415170298398</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.408064363081705</v>
       </c>
       <c r="E102">
-        <v>-53.52744450344721</v>
+        <v>-50.79349945799594</v>
       </c>
       <c r="F102">
-        <v>-2.289180211005497</v>
+        <v>-1.802928545562187</v>
       </c>
       <c r="G102">
-        <v>-6.965303832931851</v>
+        <v>-4.67926364758048</v>
       </c>
     </row>
   </sheetData>
